--- a/examples/outputs/Birgo RR Exhibits - Novav07.28.26.xlsx
+++ b/examples/outputs/Birgo RR Exhibits - Novav07.28.26.xlsx
@@ -906,13 +906,13 @@
         <v>507</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>10370</v>
+        <v>10800</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>1296.25</v>
+        <v>1350</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>2.556706114398422</v>
+        <v>2.662721893491124</v>
       </c>
       <c r="M6" s="11" t="n">
         <v>9020</v>
@@ -957,13 +957,13 @@
         <v>717.9</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>13800</v>
+        <v>16500</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>1380</v>
+        <v>1650</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>1.92227329711659</v>
+        <v>2.298370246552444</v>
       </c>
       <c r="M7" s="11" t="n">
         <v>13800</v>
@@ -1059,13 +1059,13 @@
         <v>908.0666666666667</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>93905</v>
+        <v>126000</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>1565.083333333333</v>
+        <v>2100</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>1.723533514426254</v>
+        <v>2.312605535570075</v>
       </c>
       <c r="M9" s="11" t="n">
         <v>87405</v>
@@ -1158,13 +1158,13 @@
         <v>862.2530120481928</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>129215</v>
+        <v>164440</v>
       </c>
       <c r="K11" s="17" t="n">
-        <v>1556.807228915663</v>
+        <v>1981.204819277109</v>
       </c>
       <c r="L11" s="18" t="n">
-        <v>1.805510919837355</v>
+        <v>2.297707043749214</v>
       </c>
       <c r="M11" s="17" t="n">
         <v>113985</v>
@@ -1273,7 +1273,7 @@
       <c r="E20" s="20" t="n"/>
       <c r="F20" s="20" t="n"/>
       <c r="G20" s="24" t="n">
-        <v>1550580</v>
+        <v>1973280</v>
       </c>
     </row>
     <row r="21">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="W48" s="27" t="n">
-        <v>129215</v>
+        <v>164440</v>
       </c>
     </row>
     <row r="49">
@@ -1651,16 +1651,16 @@
         <v>507</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>1296.25</v>
+        <v>1350</v>
       </c>
       <c r="K7" s="38" t="n">
-        <v>1288.571428571429</v>
+        <v>1350</v>
       </c>
       <c r="L7" s="11" t="n">
         <v>1288.571428571429</v>
       </c>
       <c r="M7" s="39" t="n">
-        <v>1</v>
+        <v>0.9544973544973546</v>
       </c>
       <c r="N7" s="38" t="n">
         <v>1283.333333333333</v>
@@ -1717,16 +1717,16 @@
         <v>717.9</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>1380</v>
+        <v>1650</v>
       </c>
       <c r="K8" s="38" t="n">
-        <v>1380</v>
+        <v>1650</v>
       </c>
       <c r="L8" s="11" t="n">
         <v>1380</v>
       </c>
       <c r="M8" s="39" t="n">
-        <v>1</v>
+        <v>0.8363636363636363</v>
       </c>
       <c r="N8" s="38" t="n">
         <v>1350</v>
@@ -1851,16 +1851,16 @@
         <v>908.0666666666667</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>1565.083333333333</v>
+        <v>2100</v>
       </c>
       <c r="K10" s="38" t="n">
-        <v>1560.803571428571</v>
+        <v>2100</v>
       </c>
       <c r="L10" s="11" t="n">
         <v>1560.803571428571</v>
       </c>
       <c r="M10" s="39" t="n">
-        <v>1</v>
+        <v>0.7432397959183673</v>
       </c>
       <c r="N10" s="38" t="n">
         <v>1532.575757575758</v>
@@ -1990,16 +1990,16 @@
         <v>862.2530120481928</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>1556.807228915663</v>
+        <v>1981.204819277109</v>
       </c>
       <c r="K12" s="42" t="n">
-        <v>1519.8</v>
+        <v>1964.133333333333</v>
       </c>
       <c r="L12" s="17" t="n">
         <v>1519.8</v>
       </c>
       <c r="M12" s="43" t="n">
-        <v>1</v>
+        <v>0.7737763899260063</v>
       </c>
       <c r="N12" s="42" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="AB65" s="27" t="n">
-        <v>129215</v>
+        <v>164440</v>
       </c>
     </row>
     <row r="66">
@@ -2292,13 +2292,13 @@
         <v>507</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>10370</v>
+        <v>10800</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>1296.25</v>
+        <v>1350</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>2.556706114398422</v>
+        <v>2.662721893491124</v>
       </c>
       <c r="M6" s="11" t="n">
         <v>9020</v>
@@ -2341,13 +2341,13 @@
         <v>717.9</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>13800</v>
+        <v>16500</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>1380</v>
+        <v>1650</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>1.92227329711659</v>
+        <v>2.298370246552444</v>
       </c>
       <c r="M7" s="11" t="n">
         <v>13800</v>
@@ -2390,13 +2390,13 @@
         <v>909.5737704918033</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>95205</v>
+        <v>127300</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>1560.737704918033</v>
+        <v>2086.885245901639</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>1.715900079302141</v>
+        <v>2.294355129406676</v>
       </c>
       <c r="M8" s="11" t="n">
         <v>88705</v>
@@ -2487,13 +2487,13 @@
         <v>862.2530120481928</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>129215</v>
+        <v>164440</v>
       </c>
       <c r="K10" s="17" t="n">
-        <v>1556.807228915663</v>
+        <v>1981.204819277109</v>
       </c>
       <c r="L10" s="18" t="n">
-        <v>1.805510919837355</v>
+        <v>2.297707043749214</v>
       </c>
       <c r="M10" s="17" t="n">
         <v>113985</v>
@@ -2604,7 +2604,7 @@
       <c r="E19" s="20" t="n"/>
       <c r="F19" s="20" t="n"/>
       <c r="G19" s="24" t="n">
-        <v>1550580</v>
+        <v>1973280</v>
       </c>
     </row>
     <row r="20">
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="U9" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V9" s="58" t="n">
         <v>1450</v>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="U10" s="58" t="n">
-        <v>1000</v>
+        <v>2100</v>
       </c>
       <c r="V10" s="58" t="n">
         <v>1000</v>
@@ -3249,7 +3249,7 @@
         </is>
       </c>
       <c r="U11" s="58" t="n">
-        <v>1625</v>
+        <v>2100</v>
       </c>
       <c r="V11" s="58" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="U12" s="58" t="n">
-        <v>1250</v>
+        <v>1650</v>
       </c>
       <c r="V12" s="58" t="n">
         <v>1250</v>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="U13" s="58" t="n">
-        <v>1200</v>
+        <v>1350</v>
       </c>
       <c r="V13" s="58" t="n">
         <v>1200</v>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="U14" s="58" t="n">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="V14" s="58" t="n">
         <v>1700</v>
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="U15" s="58" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="V15" s="58" t="n">
         <v>1550</v>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="U16" s="58" t="n">
-        <v>1200</v>
+        <v>1650</v>
       </c>
       <c r="V16" s="58" t="n">
         <v>1200</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="U17" s="58" t="n">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="V17" s="58" t="n">
         <v>1700</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="U18" s="58" t="n">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="V18" s="58" t="n">
         <v>1600</v>
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="U19" s="58" t="n">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="V19" s="58" t="n">
         <v>1600</v>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="U20" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V20" s="58" t="n">
         <v>1450</v>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="U22" s="58" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="V22" s="58" t="n">
         <v>1300</v>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="U23" s="58" t="n">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="V23" s="58" t="n">
         <v>1700</v>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="U24" s="58" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="V24" s="58" t="n">
         <v>1500</v>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="U25" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V25" s="58" t="n">
         <v>1450</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="U27" s="58" t="n">
-        <v>1350</v>
+        <v>1650</v>
       </c>
       <c r="V27" s="58" t="n">
         <v>1350</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="U28" s="58" t="n">
-        <v>1000</v>
+        <v>2100</v>
       </c>
       <c r="V28" s="58" t="n">
         <v>1000</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="U29" s="58" t="n">
-        <v>1625</v>
+        <v>2100</v>
       </c>
       <c r="V29" s="58" t="n">
         <v>0</v>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="U30" s="58" t="n">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="V30" s="58" t="n">
         <v>1750</v>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="U31" s="58" t="n">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="V31" s="58" t="n">
         <v>1600</v>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="U32" s="58" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="V32" s="58" t="n">
         <v>1550</v>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="U33" s="58" t="n">
-        <v>1400</v>
+        <v>1650</v>
       </c>
       <c r="V33" s="58" t="n">
         <v>1400</v>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="U34" s="58" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="V34" s="58" t="n">
         <v>1325</v>
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="U35" s="58" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="V35" s="58" t="n">
         <v>1550</v>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="U36" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V36" s="58" t="n">
         <v>1450</v>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="U37" s="58" t="n">
-        <v>1300</v>
+        <v>1650</v>
       </c>
       <c r="V37" s="58" t="n">
         <v>1300</v>
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="U38" s="58" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="V38" s="58" t="n">
         <v>1550</v>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="U39" s="58" t="n">
-        <v>1650</v>
+        <v>2100</v>
       </c>
       <c r="V39" s="58" t="n">
         <v>1650</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="U40" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V40" s="58" t="n">
         <v>1450</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="U41" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V41" s="58" t="n">
         <v>1450</v>
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="U43" s="58" t="n">
-        <v>1250</v>
+        <v>1350</v>
       </c>
       <c r="V43" s="58" t="n">
         <v>1250</v>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="U44" s="58" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="V44" s="58" t="n">
         <v>1550</v>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="U45" s="58" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="V45" s="58" t="n">
         <v>1550</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="U46" s="58" t="n">
-        <v>1730</v>
+        <v>2100</v>
       </c>
       <c r="V46" s="58" t="n">
         <v>1730</v>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="U48" s="58" t="n">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="V48" s="58" t="n">
         <v>1700</v>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="U49" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V49" s="58" t="n">
         <v>1450</v>
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="U50" s="58" t="n">
-        <v>1625</v>
+        <v>2100</v>
       </c>
       <c r="V50" s="58" t="n">
         <v>0</v>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="U51" s="58" t="n">
-        <v>1950</v>
+        <v>2100</v>
       </c>
       <c r="V51" s="58" t="n">
         <v>1950</v>
@@ -5761,7 +5761,7 @@
         </is>
       </c>
       <c r="U52" s="58" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="V52" s="58" t="n">
         <v>1500</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="U53" s="58" t="n">
-        <v>1400</v>
+        <v>1650</v>
       </c>
       <c r="V53" s="58" t="n">
         <v>1400</v>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="U54" s="58" t="n">
-        <v>1295</v>
+        <v>1350</v>
       </c>
       <c r="V54" s="58" t="n">
         <v>1295</v>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="U55" s="58" t="n">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="V55" s="58" t="n">
         <v>1400</v>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="U56" s="58" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="V56" s="58" t="n">
         <v>1550</v>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="U57" s="58" t="n">
-        <v>1400</v>
+        <v>1650</v>
       </c>
       <c r="V57" s="58" t="n">
         <v>1400</v>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="U58" s="58" t="n">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="V58" s="58" t="n">
         <v>1800</v>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="U59" s="58" t="n">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="V59" s="58" t="n">
         <v>1750</v>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="U60" s="58" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="V60" s="58" t="n">
         <v>1500</v>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="U61" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V61" s="58" t="n">
         <v>1450</v>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
       <c r="U63" s="58" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="V63" s="58" t="n">
         <v>1300</v>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="U64" s="58" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="V64" s="58" t="n">
         <v>1550</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="U65" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V65" s="58" t="n">
         <v>1450</v>
@@ -6629,7 +6629,7 @@
         </is>
       </c>
       <c r="U66" s="58" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="V66" s="58" t="n">
         <v>1500</v>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="U67" s="58" t="n">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="V67" s="58" t="n">
         <v>1400</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="U68" s="58" t="n">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="V68" s="58" t="n">
         <v>1800</v>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="U69" s="58" t="n">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="V69" s="58" t="n">
         <v>1750</v>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="U70" s="58" t="n">
-        <v>1950</v>
+        <v>2100</v>
       </c>
       <c r="V70" s="58" t="n">
         <v>1950</v>
@@ -6939,7 +6939,7 @@
         </is>
       </c>
       <c r="U71" s="58" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="V71" s="58" t="n">
         <v>1550</v>
@@ -7001,7 +7001,7 @@
         </is>
       </c>
       <c r="U72" s="58" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="V72" s="58" t="n">
         <v>1550</v>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="U73" s="58" t="n">
-        <v>1350</v>
+        <v>1650</v>
       </c>
       <c r="V73" s="58" t="n">
         <v>1350</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="U75" s="58" t="n">
-        <v>1350</v>
+        <v>2100</v>
       </c>
       <c r="V75" s="58" t="n">
         <v>1350</v>
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="U76" s="58" t="n">
-        <v>1650</v>
+        <v>2100</v>
       </c>
       <c r="V76" s="58" t="n">
         <v>1650</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="U77" s="58" t="n">
-        <v>1500</v>
+        <v>1650</v>
       </c>
       <c r="V77" s="58" t="n">
         <v>1500</v>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="U78" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V78" s="58" t="n">
         <v>1450</v>
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="U79" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V79" s="58" t="n">
         <v>1450</v>
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="U80" s="58" t="n">
-        <v>1625</v>
+        <v>2100</v>
       </c>
       <c r="V80" s="58" t="n">
         <v>1625</v>
@@ -7559,7 +7559,7 @@
         </is>
       </c>
       <c r="U81" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V81" s="58" t="n">
         <v>1450</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="U84" s="58" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="V84" s="58" t="n">
         <v>1550</v>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="U85" s="58" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="V85" s="58" t="n">
         <v>1550</v>
@@ -7857,7 +7857,7 @@
         </is>
       </c>
       <c r="U86" s="58" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="V86" s="58" t="n">
         <v>1500</v>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="U87" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V87" s="58" t="n">
         <v>1450</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="U88" s="58" t="n">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="V88" s="58" t="n">
         <v>1750</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="U89" s="58" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="V89" s="58" t="n">
         <v>1450</v>
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="U90" s="58" t="n">
-        <v>1625</v>
+        <v>2100</v>
       </c>
       <c r="V90" s="58" t="n">
         <v>0</v>
@@ -8148,7 +8148,7 @@
       <c r="S91" s="61" t="n"/>
       <c r="T91" s="61" t="n"/>
       <c r="U91" s="64" t="n">
-        <v>129215</v>
+        <v>164440</v>
       </c>
       <c r="V91" s="64" t="n">
         <v>113985</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="L33" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M33" s="81">
         <f>Y33</f>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="L34" s="81" t="n">
-        <v>1000</v>
+        <v>2100</v>
       </c>
       <c r="M34" s="81">
         <f>Y34</f>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="L35" s="85" t="n">
-        <v>1625</v>
+        <v>2100</v>
       </c>
       <c r="M35" s="85">
         <f>Y35</f>
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="L36" s="81" t="n">
-        <v>1250</v>
+        <v>1650</v>
       </c>
       <c r="M36" s="81">
         <f>Y36</f>
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="L37" s="81" t="n">
-        <v>1200</v>
+        <v>1350</v>
       </c>
       <c r="M37" s="81">
         <f>Y37</f>
@@ -9388,7 +9388,7 @@
         </is>
       </c>
       <c r="L38" s="81" t="n">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="M38" s="81">
         <f>Y38</f>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="L39" s="81" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="M39" s="81">
         <f>Y39</f>
@@ -9534,7 +9534,7 @@
         </is>
       </c>
       <c r="L40" s="81" t="n">
-        <v>1200</v>
+        <v>1650</v>
       </c>
       <c r="M40" s="81">
         <f>Y40</f>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="L41" s="81" t="n">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="M41" s="81">
         <f>Y41</f>
@@ -9680,7 +9680,7 @@
         </is>
       </c>
       <c r="L42" s="81" t="n">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="M42" s="81">
         <f>Y42</f>
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="L43" s="81" t="n">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="M43" s="81">
         <f>Y43</f>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="L44" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M44" s="81">
         <f>Y44</f>
@@ -9974,7 +9974,7 @@
         </is>
       </c>
       <c r="L46" s="81" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="M46" s="81">
         <f>Y46</f>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="L47" s="81" t="n">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="M47" s="81">
         <f>Y47</f>
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="L48" s="81" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="M48" s="81">
         <f>Y48</f>
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="L49" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M49" s="81">
         <f>Y49</f>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="L51" s="81" t="n">
-        <v>1350</v>
+        <v>1650</v>
       </c>
       <c r="M51" s="81">
         <f>Y51</f>
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="L52" s="81" t="n">
-        <v>1000</v>
+        <v>2100</v>
       </c>
       <c r="M52" s="81">
         <f>Y52</f>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="L53" s="85" t="n">
-        <v>1625</v>
+        <v>2100</v>
       </c>
       <c r="M53" s="85">
         <f>Y53</f>
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="L54" s="81" t="n">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="M54" s="81">
         <f>Y54</f>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="L55" s="81" t="n">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="M55" s="81">
         <f>Y55</f>
@@ -10706,7 +10706,7 @@
         </is>
       </c>
       <c r="L56" s="81" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="M56" s="81">
         <f>Y56</f>
@@ -10779,7 +10779,7 @@
         </is>
       </c>
       <c r="L57" s="81" t="n">
-        <v>1400</v>
+        <v>1650</v>
       </c>
       <c r="M57" s="81">
         <f>Y57</f>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="L58" s="81" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="M58" s="81">
         <f>Y58</f>
@@ -10925,7 +10925,7 @@
         </is>
       </c>
       <c r="L59" s="81" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="M59" s="81">
         <f>Y59</f>
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="L60" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M60" s="81">
         <f>Y60</f>
@@ -11071,7 +11071,7 @@
         </is>
       </c>
       <c r="L61" s="81" t="n">
-        <v>1300</v>
+        <v>1650</v>
       </c>
       <c r="M61" s="81">
         <f>Y61</f>
@@ -11144,7 +11144,7 @@
         </is>
       </c>
       <c r="L62" s="81" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="M62" s="81">
         <f>Y62</f>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="L63" s="81" t="n">
-        <v>1650</v>
+        <v>2100</v>
       </c>
       <c r="M63" s="81">
         <f>Y63</f>
@@ -11290,7 +11290,7 @@
         </is>
       </c>
       <c r="L64" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M64" s="81">
         <f>Y64</f>
@@ -11363,7 +11363,7 @@
         </is>
       </c>
       <c r="L65" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M65" s="81">
         <f>Y65</f>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="L67" s="81" t="n">
-        <v>1250</v>
+        <v>1350</v>
       </c>
       <c r="M67" s="81">
         <f>Y67</f>
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="L68" s="81" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="M68" s="81">
         <f>Y68</f>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="L69" s="81" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="M69" s="81">
         <f>Y69</f>
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="L70" s="81" t="n">
-        <v>1730</v>
+        <v>2100</v>
       </c>
       <c r="M70" s="81">
         <f>Y70</f>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="L72" s="81" t="n">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="M72" s="81">
         <f>Y72</f>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="L73" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M73" s="81">
         <f>Y73</f>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="L74" s="85" t="n">
-        <v>1625</v>
+        <v>2100</v>
       </c>
       <c r="M74" s="85">
         <f>Y74</f>
@@ -12097,7 +12097,7 @@
         </is>
       </c>
       <c r="L75" s="81" t="n">
-        <v>1950</v>
+        <v>2100</v>
       </c>
       <c r="M75" s="81">
         <f>Y75</f>
@@ -12170,7 +12170,7 @@
         </is>
       </c>
       <c r="L76" s="81" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="M76" s="81">
         <f>Y76</f>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="L77" s="81" t="n">
-        <v>1400</v>
+        <v>1650</v>
       </c>
       <c r="M77" s="81">
         <f>Y77</f>
@@ -12316,7 +12316,7 @@
         </is>
       </c>
       <c r="L78" s="81" t="n">
-        <v>1295</v>
+        <v>1350</v>
       </c>
       <c r="M78" s="81">
         <f>Y78</f>
@@ -12389,7 +12389,7 @@
         </is>
       </c>
       <c r="L79" s="81" t="n">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="M79" s="81">
         <f>Y79</f>
@@ -12462,7 +12462,7 @@
         </is>
       </c>
       <c r="L80" s="81" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="M80" s="81">
         <f>Y80</f>
@@ -12535,7 +12535,7 @@
         </is>
       </c>
       <c r="L81" s="81" t="n">
-        <v>1400</v>
+        <v>1650</v>
       </c>
       <c r="M81" s="81">
         <f>Y81</f>
@@ -12608,7 +12608,7 @@
         </is>
       </c>
       <c r="L82" s="81" t="n">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="M82" s="81">
         <f>Y82</f>
@@ -12681,7 +12681,7 @@
         </is>
       </c>
       <c r="L83" s="81" t="n">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="M83" s="81">
         <f>Y83</f>
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="L84" s="81" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="M84" s="81">
         <f>Y84</f>
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="L85" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M85" s="81">
         <f>Y85</f>
@@ -12973,7 +12973,7 @@
         </is>
       </c>
       <c r="L87" s="81" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="M87" s="81">
         <f>Y87</f>
@@ -13046,7 +13046,7 @@
         </is>
       </c>
       <c r="L88" s="81" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="M88" s="81">
         <f>Y88</f>
@@ -13119,7 +13119,7 @@
         </is>
       </c>
       <c r="L89" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M89" s="81">
         <f>Y89</f>
@@ -13192,7 +13192,7 @@
         </is>
       </c>
       <c r="L90" s="81" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="M90" s="81">
         <f>Y90</f>
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="L91" s="81" t="n">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="M91" s="81">
         <f>Y91</f>
@@ -13338,7 +13338,7 @@
         </is>
       </c>
       <c r="L92" s="81" t="n">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="M92" s="81">
         <f>Y92</f>
@@ -13411,7 +13411,7 @@
         </is>
       </c>
       <c r="L93" s="81" t="n">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="M93" s="81">
         <f>Y93</f>
@@ -13484,7 +13484,7 @@
         </is>
       </c>
       <c r="L94" s="81" t="n">
-        <v>1950</v>
+        <v>2100</v>
       </c>
       <c r="M94" s="81">
         <f>Y94</f>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="L95" s="81" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="M95" s="81">
         <f>Y95</f>
@@ -13630,7 +13630,7 @@
         </is>
       </c>
       <c r="L96" s="81" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="M96" s="81">
         <f>Y96</f>
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="L97" s="81" t="n">
-        <v>1350</v>
+        <v>1650</v>
       </c>
       <c r="M97" s="81">
         <f>Y97</f>
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="L99" s="81" t="n">
-        <v>1350</v>
+        <v>2100</v>
       </c>
       <c r="M99" s="81">
         <f>Y99</f>
@@ -13922,7 +13922,7 @@
         </is>
       </c>
       <c r="L100" s="81" t="n">
-        <v>1650</v>
+        <v>2100</v>
       </c>
       <c r="M100" s="81">
         <f>Y100</f>
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="L101" s="81" t="n">
-        <v>1500</v>
+        <v>1650</v>
       </c>
       <c r="M101" s="81">
         <f>Y101</f>
@@ -14068,7 +14068,7 @@
         </is>
       </c>
       <c r="L102" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M102" s="81">
         <f>Y102</f>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="L103" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M103" s="81">
         <f>Y103</f>
@@ -14214,7 +14214,7 @@
         </is>
       </c>
       <c r="L104" s="81" t="n">
-        <v>1625</v>
+        <v>2100</v>
       </c>
       <c r="M104" s="81">
         <f>Y104</f>
@@ -14287,7 +14287,7 @@
         </is>
       </c>
       <c r="L105" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M105" s="81">
         <f>Y105</f>
@@ -14510,7 +14510,7 @@
         </is>
       </c>
       <c r="L108" s="81" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="M108" s="81">
         <f>Y108</f>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="L109" s="81" t="n">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="M109" s="81">
         <f>Y109</f>
@@ -14656,7 +14656,7 @@
         </is>
       </c>
       <c r="L110" s="81" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="M110" s="81">
         <f>Y110</f>
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="L111" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M111" s="81">
         <f>Y111</f>
@@ -14802,7 +14802,7 @@
         </is>
       </c>
       <c r="L112" s="81" t="n">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="M112" s="81">
         <f>Y112</f>
@@ -14875,7 +14875,7 @@
         </is>
       </c>
       <c r="L113" s="81" t="n">
-        <v>1450</v>
+        <v>2100</v>
       </c>
       <c r="M113" s="81">
         <f>Y113</f>
@@ -14948,7 +14948,7 @@
         </is>
       </c>
       <c r="L114" s="85" t="n">
-        <v>1625</v>
+        <v>2100</v>
       </c>
       <c r="M114" s="85">
         <f>Y114</f>
